--- a/src/test/resources/FlightSaudiadata.xlsx
+++ b/src/test/resources/FlightSaudiadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ravibhushan.Kumar\eclipse-workspace\Project_SAUDIA\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6159542-987F-4305-91EA-86018BFA64C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949242F4-5502-4B5D-AC03-DD8C9ADA4A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14040" xr2:uid="{7DC593AB-2AC3-4143-ABC1-B9CC8773C1AC}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="80">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -186,9 +186,6 @@
     <t>Multi-city</t>
   </si>
   <si>
-    <t>25-Sep-2026</t>
-  </si>
-  <si>
     <t>TC-03:-Verify user is able to create booking</t>
   </si>
   <si>
@@ -252,22 +249,37 @@
     <t>PASS34217</t>
   </si>
   <si>
-    <t>27-Sep-2026</t>
-  </si>
-  <si>
-    <t>29-Sep-2026</t>
-  </si>
-  <si>
-    <t>26-Sep-2026</t>
-  </si>
-  <si>
-    <t>28-Sep-2026</t>
-  </si>
-  <si>
     <t>Balashewar</t>
   </si>
   <si>
     <t>saket</t>
+  </si>
+  <si>
+    <t>12-Oct-2026</t>
+  </si>
+  <si>
+    <t>14-Oct-2026</t>
+  </si>
+  <si>
+    <t>16-Oct-2026</t>
+  </si>
+  <si>
+    <t>17-Oct-2026</t>
+  </si>
+  <si>
+    <t>19-Oct-2026</t>
+  </si>
+  <si>
+    <t>21-Oct-2026</t>
+  </si>
+  <si>
+    <t>18-Oct-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Family trip </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Employee  </t>
   </si>
 </sst>
 </file>
@@ -763,7 +775,7 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
@@ -775,14 +787,14 @@
         <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>12</v>
@@ -796,19 +808,19 @@
         <v>40</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U2" s="1" t="s">
         <v>26</v>
@@ -820,19 +832,19 @@
         <v>40</v>
       </c>
       <c r="X2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="AA2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>41</v>
@@ -850,178 +862,104 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CCE6EC1-6C99-4FA8-9E5E-FE50AE294D93}">
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>61</v>
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="L1" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>57</v>
+        <v>39</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>9</v>
@@ -1033,27 +971,80 @@
         <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>16</v>
@@ -1062,11 +1053,11 @@
         <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>11</v>
@@ -1074,15 +1065,70 @@
       <c r="I4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -1091,9 +1137,11 @@
         <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="1"/>
+        <v>72</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="G5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1102,17 +1150,11 @@
       </c>
       <c r="I5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>18</v>
@@ -1124,11 +1166,11 @@
         <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>11</v>
@@ -1138,40 +1180,13 @@
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
-      <c r="L6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>16</v>
@@ -1180,13 +1195,11 @@
         <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>73</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>11</v>
@@ -1194,33 +1207,298 @@
       <c r="I7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1" t="s">
+      <c r="J7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="P8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="S9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R14" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="S14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="S7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="U7" s="1" t="s">
+      <c r="U15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V7" s="1" t="s">
+      <c r="V15" s="1" t="s">
         <v>27</v>
       </c>
     </row>

--- a/src/test/resources/FlightSaudiadata.xlsx
+++ b/src/test/resources/FlightSaudiadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ravibhushan.Kumar\eclipse-workspace\Project_SAUDIA\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{949242F4-5502-4B5D-AC03-DD8C9ADA4A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D3A23E-F11C-4D71-8B08-3F6E03154401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14040" xr2:uid="{7DC593AB-2AC3-4143-ABC1-B9CC8773C1AC}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="121">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -186,100 +186,223 @@
     <t>Multi-city</t>
   </si>
   <si>
+    <t>TC-06:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t>Krishna</t>
+  </si>
+  <si>
+    <t>24-Sep-2005</t>
+  </si>
+  <si>
+    <t>PASS3421</t>
+  </si>
+  <si>
+    <t>Sudah</t>
+  </si>
+  <si>
+    <t>Kant</t>
+  </si>
+  <si>
+    <t>15-Sep-2001</t>
+  </si>
+  <si>
+    <t>PASS34025</t>
+  </si>
+  <si>
+    <t>TC-04:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-02:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Baleshwar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-08:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>Rajvir</t>
+  </si>
+  <si>
+    <t>24-Sep-2006</t>
+  </si>
+  <si>
+    <t>PASS342523</t>
+  </si>
+  <si>
+    <t>PASS34217</t>
+  </si>
+  <si>
+    <t>Balashewar</t>
+  </si>
+  <si>
+    <t>saket</t>
+  </si>
+  <si>
+    <t>12-Oct-2026</t>
+  </si>
+  <si>
+    <t>14-Oct-2026</t>
+  </si>
+  <si>
+    <t>16-Oct-2026</t>
+  </si>
+  <si>
+    <t>17-Oct-2026</t>
+  </si>
+  <si>
+    <t>19-Oct-2026</t>
+  </si>
+  <si>
+    <t>21-Oct-2026</t>
+  </si>
+  <si>
+    <t>18-Oct-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-03:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>TC-07:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-09:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Family trip </t>
+  </si>
+  <si>
+    <t>paymentMethod</t>
+  </si>
+  <si>
+    <t>CardNumber</t>
+  </si>
+  <si>
+    <t>CardHolderName</t>
+  </si>
+  <si>
+    <t>SecurityCode</t>
+  </si>
+  <si>
+    <t>Saved cards</t>
+  </si>
+  <si>
+    <t>4111-1111-1111-1111</t>
+  </si>
+  <si>
+    <t>Ravi bhushan</t>
+  </si>
+  <si>
+    <t>Expirymonth</t>
+  </si>
+  <si>
+    <t>ExpiryYear</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>2034</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>Use a different card</t>
+  </si>
+  <si>
+    <t>TC-01:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t>TC-02:-Verify user is able to create booking</t>
+  </si>
+  <si>
     <t>TC-03:-Verify user is able to create booking</t>
   </si>
   <si>
-    <t>TC-06:-Verify user is able to create booking</t>
-  </si>
-  <si>
-    <t>Bal</t>
-  </si>
-  <si>
-    <t>Krishna</t>
-  </si>
-  <si>
-    <t>24-Sep-2005</t>
-  </si>
-  <si>
-    <t>PASS3421</t>
-  </si>
-  <si>
-    <t>Sudah</t>
-  </si>
-  <si>
-    <t>Kant</t>
-  </si>
-  <si>
-    <t>15-Sep-2001</t>
-  </si>
-  <si>
-    <t>PASS34025</t>
-  </si>
-  <si>
-    <t>TC-04:-Verify user is able to create booking</t>
+    <t xml:space="preserve">TC-04:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-05:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>TC-08:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-10:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>SADAD</t>
+  </si>
+  <si>
+    <t>OTP</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-06:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>20-Oct-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-07:-Verify user is able to create booking </t>
   </si>
   <si>
     <t xml:space="preserve">TC-01:-Verify user is able to create booking </t>
   </si>
   <si>
-    <t xml:space="preserve">TC-02:-Verify user is able to create booking </t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-07:-Verify user is able to create booking </t>
-  </si>
-  <si>
-    <t>Baleshwar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-08:-Verify user is able to create booking </t>
-  </si>
-  <si>
-    <t>Rajvir</t>
-  </si>
-  <si>
-    <t>24-Sep-2006</t>
-  </si>
-  <si>
-    <t>PASS342523</t>
-  </si>
-  <si>
-    <t>PASS34217</t>
-  </si>
-  <si>
-    <t>Balashewar</t>
-  </si>
-  <si>
-    <t>saket</t>
-  </si>
-  <si>
-    <t>12-Oct-2026</t>
-  </si>
-  <si>
-    <t>14-Oct-2026</t>
-  </si>
-  <si>
-    <t>16-Oct-2026</t>
-  </si>
-  <si>
-    <t>17-Oct-2026</t>
-  </si>
-  <si>
-    <t>19-Oct-2026</t>
-  </si>
-  <si>
-    <t>21-Oct-2026</t>
-  </si>
-  <si>
-    <t>18-Oct-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Family trip </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Employee  </t>
+    <t>23-Oct-2026</t>
+  </si>
+  <si>
+    <t>22-Oct-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-11:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-12:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>TC-14:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-18:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-19:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-20:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>TC-22:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t>TC-13:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-15:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>TC-16:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-17:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>TC-21:-Verify user is able to create booking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-23:-Verify user is able to create booking </t>
+  </si>
+  <si>
+    <t>TC-24:-Verify user is able to create booking</t>
   </si>
 </sst>
 </file>
@@ -659,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4775AB72-AEA3-4520-9C23-DEE07D8ADD12}">
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.85546875" customWidth="1"/>
@@ -679,9 +802,14 @@
     <col min="28" max="28" width="16.42578125" customWidth="1"/>
     <col min="29" max="29" width="18.85546875" customWidth="1"/>
     <col min="30" max="30" width="22.85546875" customWidth="1"/>
+    <col min="31" max="31" width="16.42578125" customWidth="1"/>
+    <col min="32" max="32" width="21.42578125" customWidth="1"/>
+    <col min="33" max="33" width="15.28515625" customWidth="1"/>
+    <col min="34" max="34" width="16.42578125" customWidth="1"/>
+    <col min="35" max="35" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -772,10 +900,31 @@
       <c r="AD1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>18</v>
@@ -787,14 +936,14 @@
         <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>12</v>
@@ -808,19 +957,19 @@
         <v>40</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="U2" s="1" t="s">
         <v>26</v>
@@ -832,25 +981,1685 @@
         <v>40</v>
       </c>
       <c r="X2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB2" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>41</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>27</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK5" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK6" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE9" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ10" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK11" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK13" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK14" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH15" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ15" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ16" s="1"/>
+      <c r="AK16" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE17" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ18" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK19" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ20" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK21" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK22" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ23" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ24" s="1"/>
+      <c r="AK24" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE25" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -862,10 +2671,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CCE6EC1-6C99-4FA8-9E5E-FE50AE294D93}">
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:AK37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="83" customWidth="1"/>
+    <col min="10" max="10" width="29.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -957,9 +2770,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>9</v>
@@ -971,16 +2784,16 @@
         <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>12</v>
@@ -994,19 +2807,19 @@
         <v>40</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="Q3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="U3" s="1" t="s">
         <v>26</v>
@@ -1018,19 +2831,19 @@
         <v>40</v>
       </c>
       <c r="X3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB3" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="AC3" s="1" t="s">
         <v>41</v>
@@ -1039,12 +2852,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>16</v>
@@ -1053,9 +2866,11 @@
         <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F4" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="G4" s="1" t="s">
         <v>19</v>
       </c>
@@ -1065,12 +2880,8 @@
       <c r="I4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
       <c r="L4" s="1" t="s">
         <v>20</v>
       </c>
@@ -1078,19 +2889,19 @@
         <v>40</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="U4" s="1" t="s">
         <v>26</v>
@@ -1102,19 +2913,19 @@
         <v>40</v>
       </c>
       <c r="X4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB4" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="AC4" s="1" t="s">
         <v>41</v>
@@ -1123,12 +2934,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
@@ -1137,13 +2948,11 @@
         <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>73</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>11</v>
@@ -1151,13 +2960,70 @@
       <c r="I5" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="J5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>16</v>
@@ -1166,9 +3032,11 @@
         <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="G6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1178,15 +3046,13 @@
       <c r="I6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>16</v>
@@ -1195,7 +3061,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1" t="s">
@@ -1207,19 +3073,15 @@
       <c r="I7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
@@ -1228,11 +3090,11 @@
         <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>11</v>
@@ -1240,42 +3102,19 @@
       <c r="I8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="J8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>16</v>
@@ -1284,13 +3123,11 @@
         <v>17</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>76</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>11</v>
@@ -1301,25 +3138,25 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>40</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="U9" s="1" t="s">
         <v>26</v>
@@ -1328,8 +3165,105 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="AE11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1"/>
+      <c r="AH11" s="1"/>
+      <c r="AI11" s="1"/>
+      <c r="AJ11" s="1"/>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
@@ -1340,7 +3274,7 @@
         <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
@@ -1354,99 +3288,28 @@
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>9</v>
@@ -1458,10 +3321,10 @@
         <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>19</v>
@@ -1475,31 +3338,1220 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="Q15" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>23</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="U15" s="1" t="s">
         <v>26</v>
       </c>
       <c r="V15" s="1" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ23" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ24" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ25" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG26" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI26" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ26" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="AE27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG27" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH27" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI27" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ27" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE28" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI28" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ28" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE29" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z31" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH31" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE32" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V33" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y33" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD33" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH33" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y34" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE34" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK35" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE36" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ36" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB37" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AJ37" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/FlightSaudiadata.xlsx
+++ b/src/test/resources/FlightSaudiadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ravibhushan.Kumar\eclipse-workspace\Project_SAUDIA\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E043C9C-09E1-4999-B892-D0A2FAC0D1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFFAACB-6D9F-433C-A65F-A492BAC34EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14040" xr2:uid="{7DC593AB-2AC3-4143-ABC1-B9CC8773C1AC}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="144">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -285,99 +285,9 @@
     <t>Priority</t>
   </si>
   <si>
-    <t>Ravi Kumar;Sudhir Kumar;Nirman Kumar;Rahul Kumar</t>
-  </si>
-  <si>
-    <t>Adult-1;Adult-2;Child-1;Adult-1</t>
-  </si>
-  <si>
-    <t>Adult-1;Adult-2;Child-1</t>
-  </si>
-  <si>
-    <t>Ravi Kumar;Sudhir Kumar;Nirman Kumar</t>
-  </si>
-  <si>
-    <t>TC-01:-Verify Admin user is able to create booking  for One way of Family</t>
-  </si>
-  <si>
-    <t>TC-02:-Verify Admin user is able to create booking for  One way of Family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-03:-Verify Admin user is able to create booking for One way of Guest traveler </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-04:-Verify  Admin user is able to create booking for One way of Guest traveler </t>
-  </si>
-  <si>
-    <t>TC-05:-Verify Admin user is able to create booking for One way of Employee</t>
-  </si>
-  <si>
-    <t>TC-06:-Verify Admin user is able to create booking for One way of Employee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-07:-Verify Admin user is able to create booking  for One way of Guest traveler </t>
-  </si>
-  <si>
-    <t>TC-08:-Verify Admin user is able to create booking for One way of Employee</t>
-  </si>
-  <si>
-    <t>TC-15:-Verify Admin user is able to create booking for Round Trip of Guest Traveller</t>
-  </si>
-  <si>
     <t>Dependent Name/Traveler's list</t>
   </si>
   <si>
-    <t>Round Trip</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Multiple travelers </t>
-  </si>
-  <si>
-    <t>Multiple travelers</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Raushan Kumar;Sumit Kumar</t>
-  </si>
-  <si>
-    <t>Adult-1;Adult-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-09:-Verify Admin user is able to create booking for One way of  Multiple travelers  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-10:-Verify Admin user is able to create booking for One way of  Multiple travelers  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-20:-Verify Admin user is able to create booking for Round Trip of  Multiple travelers  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TC-21:-Verify Admin user is able to create booking for Round Trip of  Multiple travelers  </t>
-  </si>
-  <si>
-    <t>TC-22:-Verify Admin user is able to create booking for Multi-city of Family Trip</t>
-  </si>
-  <si>
-    <t>TC-23:-Verify Admin user is able to create booking for Multi-city of Family Trip</t>
-  </si>
-  <si>
-    <t>TC-24:-Verify Admin user is able to create booking for Multi-city of Guest Traveller</t>
-  </si>
-  <si>
-    <t>TC-25:-Verify Admin user is able to create booking for Multi-city of Guest Traveller</t>
-  </si>
-  <si>
-    <t>TC-26:-Verify Admin user is able to create booking for Multi-city of Employee</t>
-  </si>
-  <si>
-    <t>TC-27:-Verify Adminuser is able to create booking for Multi-city of Employee</t>
-  </si>
-  <si>
-    <t>TC-28:-Verify Admin user is able to create booking  for Multi-city of Guest Traveller</t>
-  </si>
-  <si>
-    <t>TC-29:-Verify Admin user is able to create booking for Multi-city of Employee</t>
-  </si>
-  <si>
     <t xml:space="preserve">Madinah, Saudi Arabia </t>
   </si>
   <si>
@@ -396,18 +306,12 @@
     <t>27-Oct-2026</t>
   </si>
   <si>
-    <t>29-Oct-2026</t>
-  </si>
-  <si>
     <t>26-Oct-2026</t>
   </si>
   <si>
     <t>MultiCityTo</t>
   </si>
   <si>
-    <t xml:space="preserve"> Jeddah,Saudi Arabia ; Riyadh, Saudi Arabia</t>
-  </si>
-  <si>
     <t>MultiCityDepartureDate</t>
   </si>
   <si>
@@ -438,9 +342,6 @@
     <t>London, United Kingdom ;Jeddah,Saudi Arabia</t>
   </si>
   <si>
-    <t>Madinah, Saudi Arabia;Riyadh, Saudi Arabia</t>
-  </si>
-  <si>
     <t>27-Oct-2026;29-Oct-2026</t>
   </si>
   <si>
@@ -456,51 +357,6 @@
     <t>18-Oct-2026;20-Oct-2026</t>
   </si>
   <si>
-    <t>TC-09:-Verify Admin user is able to create booking for Round Trip of FamilyTrip</t>
-  </si>
-  <si>
-    <t>TC-10:-Verify Admin user is able to create booking for Round Trip of FamilyTrip</t>
-  </si>
-  <si>
-    <t>TC-11:-Verify Admin user is able to create booking for Round Trip of Guest Traveller</t>
-  </si>
-  <si>
-    <t>TC-12:-Verify Admin user is able to create booking for Round Trip of Guest Traveller</t>
-  </si>
-  <si>
-    <t>TC-13:-Verify Admin user is able to create booking  for Round Trip of Employee</t>
-  </si>
-  <si>
-    <t>TC-14:-Verify Admin user is able to create booking for Round Trip of Employee</t>
-  </si>
-  <si>
-    <t>TC-16:-Verify Admin user is able to create booking for Multi-city of Employee</t>
-  </si>
-  <si>
-    <t>TC-17:-Verify Admin user is able to create booking for Multi-city of Family Trip</t>
-  </si>
-  <si>
-    <t>TC-18:-Verify Admin user is able to create booking for Multi-city of Family Trip</t>
-  </si>
-  <si>
-    <t>TC-19:-Verify Admin user is able to create booking for Multi-city of Guest Traveller</t>
-  </si>
-  <si>
-    <t>TC-20:-Verify Admin user is able to create booking for Multi-city of Guest Traveller</t>
-  </si>
-  <si>
-    <t>TC-21:-Verify Admin user is able to create booking for Multi-city of Employee</t>
-  </si>
-  <si>
-    <t>TC-22:-Verify Adminuser is able to create booking for Multi-city of Employee</t>
-  </si>
-  <si>
-    <t>TC-23:-Verify Admin user is able to create booking  for Multi-city of Guest Traveller</t>
-  </si>
-  <si>
-    <t>TC-24:-Verify Admin user is able to create booking for Multi-city of Employee</t>
-  </si>
-  <si>
     <t>Tushar;Anu;Anant;</t>
   </si>
   <si>
@@ -511,6 +367,111 @@
   </si>
   <si>
     <t>Tushar;Anu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madinah, Saudi Arabia ;Riyadh, Saudi Arabia </t>
+  </si>
+  <si>
+    <t>Tushar;Anu;Anant</t>
+  </si>
+  <si>
+    <t>Tushar;Anu;</t>
+  </si>
+  <si>
+    <t>TC-01:-Verify Admin user is able to create booking for Round Trip of FamilyTrip</t>
+  </si>
+  <si>
+    <t>TC-02:-Verify Admin user is able to create booking for Round Trip of FamilyTrip</t>
+  </si>
+  <si>
+    <t>TC-03:-Verify Admin user is able to create booking for Round Trip of Guest Traveller</t>
+  </si>
+  <si>
+    <t>TC-04:-Verify Admin user is able to create booking for Round Trip of Guest Traveller</t>
+  </si>
+  <si>
+    <t>TC-05:-Verify Admin user is able to create booking  for Round Trip of Employee</t>
+  </si>
+  <si>
+    <t>TC-06:-Verify Admin user is able to create booking for Round Trip of Employee</t>
+  </si>
+  <si>
+    <t>TC-07:-Verify Admin user is able to create booking for Round Trip of Guest Traveller</t>
+  </si>
+  <si>
+    <t>TC-08:-Verify Admin user is able to create booking for Multi-city of Family Trip</t>
+  </si>
+  <si>
+    <t>TC-10:-Verify Admin user is able to create booking for Multi-city of Guest Traveller</t>
+  </si>
+  <si>
+    <t>TC-09:-Verify Admin user is able to create booking for Multi-city of Family Trip</t>
+  </si>
+  <si>
+    <t>TC-11:-Verify Admin user is able to create booking for Multi-city of Guest Traveller</t>
+  </si>
+  <si>
+    <t>TC-12:-Verify Admin user is able to create booking for Multi-city of Employee</t>
+  </si>
+  <si>
+    <t>TC-13:-Verify Adminuser is able to create booking for Multi-city of Employee</t>
+  </si>
+  <si>
+    <t>TC-14:-Verify Admin user is able to create booking  for Multi-city of Guest Traveller</t>
+  </si>
+  <si>
+    <t>TC-15:-Verify Admin user is able to create booking for Multi-city of Employee</t>
+  </si>
+  <si>
+    <t>TC-16:-Verify Admin user is able to create booking for Multi-city of Guest Traveller</t>
+  </si>
+  <si>
+    <t>TC-17:-Verify Admin user is able to create booking for Multi-city of Employee</t>
+  </si>
+  <si>
+    <t>TC-18:-Verify Adminuser is able to create booking for Multi-city of Employee</t>
+  </si>
+  <si>
+    <t>TC-19:-Verify Admin user is able to create booking  for Multi-city of Guest Traveller</t>
+  </si>
+  <si>
+    <t>TC-20:-Verify Admin user is able to create booking for Multi-city of Employee</t>
+  </si>
+  <si>
+    <t>TC-21:-Verify Admin user is able to create booking  for One way of Family</t>
+  </si>
+  <si>
+    <t>TC-22:-Verify Admin user is able to create booking for  One way of Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-23:-Verify Admin user is able to create booking for One way of Guest traveler </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-24:-Verify  Admin user is able to create booking for One way of Guest traveler </t>
+  </si>
+  <si>
+    <t>TC-25:-Verify Admin user is able to create booking for One way of Employee</t>
+  </si>
+  <si>
+    <t>TC-26:-Verify Admin user is able to create booking for One way of Employee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-27:-Verify Admin user is able to create booking  for One way of Guest traveler </t>
+  </si>
+  <si>
+    <t>TC-28:-Verify Admin user is able to create booking for One way of Employee</t>
+  </si>
+  <si>
+    <t>Use a different card,SADAD,Saved cards</t>
+  </si>
+  <si>
+    <t>SADAD|Use a different card</t>
+  </si>
+  <si>
+    <t>PNR</t>
+  </si>
+  <si>
+    <t>SADAD|Saved cards</t>
   </si>
 </sst>
 </file>
@@ -890,7 +851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4775AB72-AEA3-4520-9C23-DEE07D8ADD12}">
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:AN34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="74" customWidth="1"/>
@@ -902,6 +863,7 @@
     <col min="9" max="9" width="26.42578125" customWidth="1"/>
     <col min="10" max="10" width="43.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="26.42578125" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" customWidth="1"/>
     <col min="15" max="17" width="16.5703125" customWidth="1"/>
     <col min="18" max="18" width="14.140625" customWidth="1"/>
     <col min="19" max="19" width="17.28515625" customWidth="1"/>
@@ -913,8 +875,8 @@
     <col min="29" max="29" width="18.85546875" customWidth="1"/>
     <col min="30" max="30" width="22.85546875" customWidth="1"/>
     <col min="31" max="31" width="71" customWidth="1"/>
-    <col min="32" max="32" width="29.5703125" customWidth="1"/>
-    <col min="33" max="33" width="16.42578125" customWidth="1"/>
+    <col min="32" max="32" width="51.7109375" customWidth="1"/>
+    <col min="33" max="33" width="23.7109375" customWidth="1"/>
     <col min="34" max="34" width="21.42578125" customWidth="1"/>
     <col min="35" max="35" width="15.28515625" customWidth="1"/>
     <col min="36" max="36" width="16.42578125" customWidth="1"/>
@@ -950,10 +912,10 @@
         <v>6</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>13</v>
@@ -1013,7 +975,7 @@
         <v>32</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>80</v>
@@ -1039,13 +1001,16 @@
       <c r="AM1" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="AN1" s="1" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>16</v>
@@ -1056,7 +1021,9 @@
       <c r="E2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="1"/>
+      <c r="F2" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1094,13 +1061,13 @@
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1" t="s">
-        <v>153</v>
+        <v>105</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>154</v>
+        <v>106</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="AH2" s="1" t="s">
         <v>64</v>
@@ -1120,21 +1087,23 @@
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="1"/>
+      <c r="F3" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1144,9 +1113,7 @@
       <c r="I3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>124</v>
-      </c>
+      <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
         <v>20</v>
@@ -1171,38 +1138,38 @@
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
       <c r="AE3" s="1" t="s">
-        <v>156</v>
+        <v>108</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>155</v>
+        <v>107</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="AM3" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="AN3" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="AN3" s="1"/>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="F4" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="G4" s="1" t="s">
         <v>19</v>
       </c>
@@ -1213,9 +1180,7 @@
         <v>12</v>
       </c>
       <c r="J4" s="1"/>
-      <c r="K4" s="1" t="s">
-        <v>124</v>
-      </c>
+      <c r="K4" s="1"/>
       <c r="L4" s="1" t="s">
         <v>20</v>
       </c>
@@ -1270,7 +1235,7 @@
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
       <c r="AG4" s="1" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="AH4" s="1" t="s">
         <v>64</v>
@@ -1290,21 +1255,23 @@
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="1"/>
+      <c r="F5" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="G5" s="1" t="s">
         <v>19</v>
       </c>
@@ -1370,7 +1337,7 @@
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
       <c r="AG5" s="1" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="AM5" s="1" t="s">
         <v>74</v>
@@ -1378,10 +1345,10 @@
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>16</v>
@@ -1392,7 +1359,9 @@
       <c r="E6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="G6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1402,10 +1371,9 @@
       <c r="I6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="AG6" s="1" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="AM6" s="1" t="s">
         <v>74</v>
@@ -1413,21 +1381,23 @@
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="1"/>
+        <v>78</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="G7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1437,10 +1407,8 @@
       <c r="I7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
       <c r="AG7" s="1" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="AH7" s="1" t="s">
         <v>64</v>
@@ -1460,21 +1428,23 @@
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" s="1"/>
+        <v>75</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="G8" s="1" t="s">
         <v>19</v>
       </c>
@@ -1485,7 +1455,6 @@
         <v>12</v>
       </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1540,7 +1509,7 @@
       <c r="AE8" s="1"/>
       <c r="AF8" s="1"/>
       <c r="AG8" s="1" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="AL8" s="1"/>
       <c r="AM8" s="1" t="s">
@@ -1549,56 +1518,102 @@
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="AF9" s="1"/>
+      <c r="J9" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>106</v>
+      </c>
       <c r="AG9" s="1" t="s">
-        <v>72</v>
+        <v>141</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL9" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>76</v>
-      </c>
+      <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
         <v>10</v>
       </c>
@@ -1608,18 +1623,18 @@
       <c r="I10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
+      <c r="J10" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="L10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
@@ -1630,120 +1645,146 @@
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
-      <c r="Z10" s="2"/>
-      <c r="AA10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="2"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
       <c r="AE10" s="1" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK10" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL10" s="1" t="s">
-        <v>69</v>
+        <v>143</v>
+      </c>
+      <c r="AL10" s="1"/>
+      <c r="AM10" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>76</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F11" s="1"/>
       <c r="G11" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
+      <c r="J11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="L11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1"/>
-      <c r="AC11" s="1"/>
-      <c r="AD11" s="1"/>
-      <c r="AE11" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF11" s="1" t="s">
-        <v>155</v>
-      </c>
+      <c r="O11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
       <c r="AG11" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM11" s="1" t="s">
-        <v>74</v>
+        <v>141</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL11" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>77</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1753,8 +1794,12 @@
       <c r="I12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+      <c r="J12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="L12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1809,30 +1854,19 @@
       <c r="AE12" s="1"/>
       <c r="AF12" s="1"/>
       <c r="AG12" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ12" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK12" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL12" s="1" t="s">
-        <v>69</v>
+        <v>143</v>
+      </c>
+      <c r="AL12" s="1"/>
+      <c r="AM12" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>16</v>
@@ -1841,13 +1875,11 @@
         <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>77</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F13" s="1"/>
       <c r="G13" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>11</v>
@@ -1855,74 +1887,37 @@
       <c r="I13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="W13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB13" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE13" s="1"/>
-      <c r="AF13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="AG13" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM13" s="1" t="s">
-        <v>74</v>
+        <v>141</v>
+      </c>
+      <c r="AH13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL13" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>16</v>
@@ -1931,11 +1926,9 @@
         <v>17</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F14" s="1"/>
       <c r="G14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1945,35 +1938,39 @@
       <c r="I14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="AG14" s="1" t="s">
-        <v>63</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="AL14" s="1"/>
       <c r="AM14" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>117</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="F15" s="1"/>
       <c r="G15" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>11</v>
@@ -1981,8 +1978,67 @@
       <c r="I15" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="J15" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE15" s="1"/>
+      <c r="AF15" s="1"/>
       <c r="AG15" s="1" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="AH15" s="1" t="s">
         <v>64</v>
@@ -2002,25 +2058,23 @@
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>77</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>11</v>
@@ -2028,62 +2082,15 @@
       <c r="I16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J16" s="1"/>
-      <c r="L16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE16" s="1"/>
-      <c r="AF16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L16" s="1"/>
       <c r="AG16" s="1" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="AL16" s="1"/>
       <c r="AM16" s="1" t="s">
@@ -2092,25 +2099,23 @@
     </row>
     <row r="17" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>11</v>
@@ -2118,175 +2123,198 @@
       <c r="I17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K17" s="1"/>
+      <c r="J17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF17" s="1"/>
       <c r="AG17" s="1" t="s">
-        <v>72</v>
+        <v>141</v>
+      </c>
+      <c r="AH17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL17" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
-      <c r="AD18" s="1"/>
-      <c r="AE18" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="AF18" s="1" t="s">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH18" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI18" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ18" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL18" s="1" t="s">
-        <v>69</v>
+        <v>143</v>
+      </c>
+      <c r="AL18" s="1"/>
+      <c r="AM18" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>12</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
-      <c r="AD19" s="1"/>
-      <c r="AE19" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF19" s="1" t="s">
-        <v>155</v>
+        <v>79</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM19" s="1" t="s">
-        <v>74</v>
+        <v>141</v>
+      </c>
+      <c r="AH19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL19" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1" t="s">
@@ -2299,86 +2327,77 @@
         <v>12</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="O20" s="1" t="s">
+      <c r="P20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="P20" s="1" t="s">
+      <c r="Q20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="Q20" s="1" t="s">
+      <c r="R20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="R20" s="1" t="s">
+      <c r="S20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="S20" s="1" t="s">
+      <c r="T20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T20" s="1" t="s">
+      <c r="U20" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="U20" s="1" t="s">
+      <c r="V20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V20" s="1" t="s">
+      <c r="W20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="W20" s="1" t="s">
+      <c r="X20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="X20" s="1" t="s">
+      <c r="Y20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Y20" s="1" t="s">
+      <c r="Z20" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Z20" s="2" t="s">
+      <c r="AA20" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AA20" s="1" t="s">
+      <c r="AB20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AB20" s="1" t="s">
+      <c r="AC20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AC20" s="1" t="s">
+      <c r="AD20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AD20" s="1" t="s">
+      <c r="AE20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AE20" s="1"/>
       <c r="AF20" s="1"/>
       <c r="AG20" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH20" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI20" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ20" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AL20" s="1" t="s">
-        <v>69</v>
+        <v>143</v>
+      </c>
+      <c r="AL20" s="1"/>
+      <c r="AM20" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>43</v>
@@ -2390,11 +2409,11 @@
         <v>17</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>11</v>
@@ -2403,77 +2422,39 @@
         <v>12</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="W21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC21" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE21" s="1"/>
-      <c r="AF21" s="1"/>
+        <v>75</v>
+      </c>
       <c r="AG21" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM21" s="1" t="s">
-        <v>74</v>
+        <v>141</v>
+      </c>
+      <c r="AH21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL21" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>16</v>
@@ -2482,65 +2463,119 @@
         <v>17</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>135</v>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="2"/>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="1"/>
+      <c r="AD22" s="1"/>
+      <c r="AE22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AF22" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="AG22" s="1" t="s">
-        <v>63</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="AL22" s="1"/>
       <c r="AM22" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>12</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>134</v>
+        <v>92</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
+      <c r="Z23" s="2"/>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="1"/>
+      <c r="AD23" s="1"/>
+      <c r="AE23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF23" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="AG23" s="1" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="AH23" s="1" t="s">
         <v>64</v>
@@ -2560,19 +2595,19 @@
     </row>
     <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1" t="s">
@@ -2584,11 +2619,9 @@
       <c r="I24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>129</v>
-      </c>
+      <c r="J24" s="1"/>
       <c r="K24" s="1" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>20</v>
@@ -2644,7 +2677,7 @@
       <c r="AE24" s="1"/>
       <c r="AF24" s="1"/>
       <c r="AG24" s="1" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="AL24" s="1"/>
       <c r="AM24" s="1" t="s">
@@ -2653,23 +2686,23 @@
     </row>
     <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>11</v>
@@ -2677,22 +2710,86 @@
       <c r="I25" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>137</v>
-      </c>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE25" s="1"/>
+      <c r="AF25" s="1"/>
       <c r="AG25" s="1" t="s">
-        <v>72</v>
+        <v>141</v>
+      </c>
+      <c r="AH25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL25" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>16</v>
@@ -2701,13 +2798,11 @@
         <v>17</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>76</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F26" s="1"/>
       <c r="G26" s="1" t="s">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>11</v>
@@ -2715,20 +2810,22 @@
       <c r="I26" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AF26" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
       <c r="AG26" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH26" s="1"/>
+        <v>143</v>
+      </c>
+      <c r="AL26" s="1"/>
+      <c r="AM26" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>16</v>
@@ -2737,13 +2834,11 @@
         <v>17</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>76</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F27" s="1"/>
       <c r="G27" s="1" t="s">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>11</v>
@@ -2751,105 +2846,122 @@
       <c r="I27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AF27" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
       <c r="AG27" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH27" s="1"/>
+        <v>141</v>
+      </c>
+      <c r="AH27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL27" s="1" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="28" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>78</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>133</v>
-      </c>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
       <c r="L28" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="M28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="O28" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
-      <c r="AA28" s="2"/>
-      <c r="AB28" s="1"/>
-      <c r="AC28" s="1"/>
-      <c r="AD28" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD28" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="AE28" s="1"/>
-      <c r="AF28" s="1" t="s">
-        <v>81</v>
-      </c>
+      <c r="AF28" s="1"/>
       <c r="AG28" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="AH28" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI28" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ28" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL28" s="1" t="s">
-        <v>68</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="AL28" s="1"/>
       <c r="AM28" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>17</v>
@@ -2858,494 +2970,150 @@
         <v>42</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
-      <c r="AA29" s="2"/>
-      <c r="AB29" s="1"/>
-      <c r="AC29" s="1"/>
-      <c r="AD29" s="1"/>
-      <c r="AE29" s="1"/>
-      <c r="AF29" s="1" t="s">
-        <v>84</v>
-      </c>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="AF29" s="1"/>
       <c r="AG29" s="1" t="s">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="AH29" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="AI29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL29" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="AN29" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>75</v>
-      </c>
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-      <c r="G30" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="V30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="X30" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y30" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA30" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC30" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD30" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AF30" s="1"/>
-      <c r="AG30" s="1"/>
-      <c r="AH30" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI30" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK30" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL30" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="AG30" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AL30" s="1"/>
       <c r="AM30" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>56</v>
-      </c>
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
       <c r="F31" s="1"/>
-      <c r="G31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U31" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="V31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="X31" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y31" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z31" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA31" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD31" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AF31" s="1"/>
-      <c r="AG31" s="1"/>
-      <c r="AH31" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AN31" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="AH31" s="1"/>
+      <c r="AN31" s="1"/>
     </row>
     <row r="32" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
       <c r="F32" s="1"/>
-      <c r="G32" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH32" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AN32" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="AH32" s="1"/>
+      <c r="AI32" s="1"/>
+      <c r="AJ32" s="1"/>
+      <c r="AK32" s="1"/>
+      <c r="AL32" s="1"/>
+      <c r="AM32" s="1"/>
     </row>
     <row r="33" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>75</v>
-      </c>
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
       <c r="F33" s="1"/>
-      <c r="G33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH33" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ33" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK33" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL33" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AM33" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="2"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1"/>
+      <c r="AD33" s="1"/>
+      <c r="AE33" s="1"/>
+      <c r="AF33" s="1"/>
+      <c r="AG33" s="1"/>
+      <c r="AH33" s="1"/>
+      <c r="AM33" s="1"/>
+      <c r="AN33" s="1"/>
     </row>
     <row r="34" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
       <c r="F34" s="1"/>
-      <c r="G34" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R34" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="V34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W34" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="X34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y34" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA34" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC34" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE34" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AF34" s="1"/>
-      <c r="AG34" s="1"/>
-      <c r="AH34" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM34" s="1"/>
-      <c r="AN34" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH35" s="1" t="s">
-        <v>72</v>
-      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="AH34" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3356,20 +3124,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CCE6EC1-6C99-4FA8-9E5E-FE50AE294D93}">
-  <dimension ref="A1:AM44"/>
+  <dimension ref="A1:AN58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="8" max="8" width="27.140625" customWidth="1"/>
-    <col min="9" max="9" width="37.42578125" customWidth="1"/>
-    <col min="10" max="10" width="58" customWidth="1"/>
-    <col min="11" max="11" width="46.85546875" customWidth="1"/>
-    <col min="12" max="12" width="19.85546875" customWidth="1"/>
-    <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="34" max="34" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="68.28515625" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="7" max="8" width="15.85546875" customWidth="1"/>
+    <col min="9" max="9" width="26.42578125" customWidth="1"/>
+    <col min="10" max="10" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.42578125" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" customWidth="1"/>
+    <col min="15" max="17" width="16.5703125" customWidth="1"/>
+    <col min="18" max="18" width="14.140625" customWidth="1"/>
+    <col min="19" max="19" width="17.28515625" customWidth="1"/>
+    <col min="20" max="20" width="24" customWidth="1"/>
+    <col min="21" max="21" width="21.85546875" customWidth="1"/>
+    <col min="22" max="25" width="20.85546875" customWidth="1"/>
+    <col min="26" max="26" width="13.85546875" customWidth="1"/>
+    <col min="28" max="28" width="16.42578125" customWidth="1"/>
+    <col min="29" max="29" width="18.85546875" customWidth="1"/>
+    <col min="30" max="30" width="22.85546875" customWidth="1"/>
+    <col min="31" max="31" width="71" customWidth="1"/>
+    <col min="32" max="32" width="29.5703125" customWidth="1"/>
+    <col min="33" max="33" width="35.5703125" customWidth="1"/>
+    <col min="34" max="34" width="21.42578125" customWidth="1"/>
+    <col min="35" max="35" width="15.28515625" customWidth="1"/>
+    <col min="36" max="36" width="16.42578125" customWidth="1"/>
+    <col min="37" max="37" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3398,10 +3185,10 @@
         <v>6</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>13</v>
@@ -3461,7 +3248,7 @@
         <v>32</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>80</v>
@@ -3488,210 +3275,2224 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="AG6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM6" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="L8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AL8" s="1"/>
+      <c r="AM8" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="L9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AG9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL9" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="1"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AL10" s="1"/>
+      <c r="AM10" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE11" s="1"/>
+      <c r="AF11" s="1"/>
+      <c r="AG11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL11" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1"/>
+      <c r="AG12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM12" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM13" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AG14" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL14" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE15" s="1"/>
+      <c r="AF15" s="1"/>
+      <c r="AG15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AL15" s="1"/>
+      <c r="AM15" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L16" s="1"/>
+      <c r="AG16" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="T17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF17" s="1"/>
+      <c r="AG17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM17" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM18" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL19" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF20" s="1"/>
+      <c r="AG20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AL20" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG21" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H36" s="1" t="s">
+      <c r="D22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="2"/>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="1"/>
+      <c r="AD22" s="1"/>
+      <c r="AE22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AF22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AG22" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL22" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
+      <c r="Z23" s="2"/>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="1"/>
+      <c r="AD23" s="1"/>
+      <c r="AE23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF23" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM23" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1" t="s">
+      <c r="J24" s="1"/>
+      <c r="K24" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE36" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF36" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG36" s="1" t="s">
+      <c r="O24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1"/>
+      <c r="AG24" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AH36" s="1" t="s">
+      <c r="AH24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AI36" s="1" t="s">
+      <c r="AI24" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AJ36" s="1" t="s">
+      <c r="AJ24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AK36" s="1" t="s">
+      <c r="AK24" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AL36" s="1" t="s">
+      <c r="AL24" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B37" s="1" t="s">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE25" s="1"/>
+      <c r="AF25" s="1"/>
+      <c r="AG25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM25" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H37" s="1" t="s">
+      <c r="E26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J37" s="1"/>
-      <c r="L37" s="1" t="s">
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="AG26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM26" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="AG27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL27" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE37" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF37" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG37" s="1" t="s">
+      <c r="O28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1"/>
+      <c r="AG28" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AM37" s="1" t="s">
+      <c r="AL28" s="1"/>
+      <c r="AM28" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D38" s="1" t="s">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H38" s="1" t="s">
+      <c r="D29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AE38" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF38" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG38" s="1"/>
-    </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE39" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF39" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG39" s="1"/>
-    </row>
-    <row r="44" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>56</v>
-      </c>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="AF29" s="1"/>
+      <c r="AG29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN29" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="AG30" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM30" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="2"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+      <c r="AG31" s="1"/>
+      <c r="AH31" s="1"/>
+      <c r="AN31" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="AH32" s="1"/>
+      <c r="AN32" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="AH33" s="1"/>
+      <c r="AI33" s="1"/>
+      <c r="AJ33" s="1"/>
+      <c r="AK33" s="1"/>
+      <c r="AL33" s="1"/>
+      <c r="AM33" s="1"/>
+    </row>
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="2"/>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
+      <c r="AD34" s="1"/>
+      <c r="AE34" s="1"/>
+      <c r="AF34" s="1"/>
+      <c r="AG34" s="1"/>
+      <c r="AH34" s="1"/>
+      <c r="AM34" s="1"/>
+      <c r="AN34" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="AH35" s="1"/>
+    </row>
+    <row r="40" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="AG40" s="1"/>
+    </row>
+    <row r="41" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="AF41" s="1"/>
+      <c r="AG41" s="1"/>
+      <c r="AH41" s="1"/>
+    </row>
+    <row r="42" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="P42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="2"/>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
+      <c r="AD42" s="1"/>
+      <c r="AE42" s="1"/>
+      <c r="AF42" s="1"/>
+      <c r="AG42" s="1"/>
+      <c r="AH42" s="1"/>
+      <c r="AI42" s="1"/>
+      <c r="AJ42" s="1"/>
+      <c r="AK42" s="1"/>
+      <c r="AL42" s="1"/>
+      <c r="AM42" s="1"/>
+    </row>
+    <row r="43" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1"/>
+      <c r="AA43" s="2"/>
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="1"/>
+      <c r="AD43" s="1"/>
+      <c r="AE43" s="1"/>
+      <c r="AF43" s="1"/>
+      <c r="AG43" s="1"/>
+      <c r="AH43" s="1"/>
+      <c r="AM43" s="1"/>
+    </row>
+    <row r="44" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
@@ -3702,23 +5503,368 @@
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
-      <c r="Y44" s="2"/>
-      <c r="Z44" s="1"/>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="2"/>
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
-      <c r="AD44" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE44" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF44" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AL44" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="AD44" s="1"/>
+      <c r="AE44" s="1"/>
+      <c r="AF44" s="1"/>
+      <c r="AG44" s="1"/>
+      <c r="AH44" s="1"/>
+      <c r="AI44" s="1"/>
+      <c r="AJ44" s="1"/>
+      <c r="AK44" s="1"/>
+      <c r="AL44" s="1"/>
+    </row>
+    <row r="45" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="2"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="1"/>
+      <c r="AD45" s="1"/>
+      <c r="AE45" s="1"/>
+      <c r="AF45" s="1"/>
+      <c r="AG45" s="1"/>
+      <c r="AM45" s="1"/>
+    </row>
+    <row r="46" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="AG46" s="1"/>
+      <c r="AM46" s="1"/>
+    </row>
+    <row r="47" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="AG47" s="1"/>
+      <c r="AH47" s="1"/>
+      <c r="AI47" s="1"/>
+      <c r="AJ47" s="1"/>
+      <c r="AK47" s="1"/>
+      <c r="AL47" s="1"/>
+    </row>
+    <row r="48" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+      <c r="V48" s="1"/>
+      <c r="W48" s="1"/>
+      <c r="X48" s="1"/>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="2"/>
+      <c r="AA48" s="1"/>
+      <c r="AB48" s="1"/>
+      <c r="AC48" s="1"/>
+      <c r="AD48" s="1"/>
+      <c r="AE48" s="1"/>
+      <c r="AF48" s="1"/>
+      <c r="AG48" s="1"/>
+      <c r="AL48" s="1"/>
+      <c r="AM48" s="1"/>
+    </row>
+    <row r="49" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="AH49" s="1"/>
+    </row>
+    <row r="51" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+      <c r="AA51" s="2"/>
+      <c r="AB51" s="1"/>
+      <c r="AC51" s="1"/>
+      <c r="AD51" s="1"/>
+      <c r="AE51" s="1"/>
+      <c r="AF51" s="1"/>
+      <c r="AG51" s="1"/>
+      <c r="AH51" s="1"/>
+      <c r="AI51" s="1"/>
+      <c r="AJ51" s="1"/>
+      <c r="AK51" s="1"/>
+      <c r="AL51" s="1"/>
+    </row>
+    <row r="52" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1"/>
+      <c r="V52" s="1"/>
+      <c r="W52" s="1"/>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1"/>
+      <c r="Z52" s="1"/>
+      <c r="AA52" s="2"/>
+      <c r="AB52" s="1"/>
+      <c r="AC52" s="1"/>
+      <c r="AD52" s="1"/>
+      <c r="AE52" s="1"/>
+      <c r="AF52" s="1"/>
+      <c r="AG52" s="1"/>
+      <c r="AL52" s="1"/>
+      <c r="AM52" s="1"/>
+    </row>
+    <row r="53" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="1"/>
+      <c r="S53" s="1"/>
+      <c r="T53" s="1"/>
+      <c r="U53" s="1"/>
+      <c r="V53" s="1"/>
+      <c r="W53" s="1"/>
+      <c r="X53" s="1"/>
+      <c r="Y53" s="1"/>
+      <c r="Z53" s="2"/>
+      <c r="AA53" s="1"/>
+      <c r="AB53" s="1"/>
+      <c r="AC53" s="1"/>
+      <c r="AD53" s="1"/>
+      <c r="AE53" s="1"/>
+      <c r="AF53" s="1"/>
+      <c r="AG53" s="1"/>
+      <c r="AH53" s="1"/>
+      <c r="AI53" s="1"/>
+      <c r="AJ53" s="1"/>
+      <c r="AK53" s="1"/>
+      <c r="AL53" s="1"/>
+    </row>
+    <row r="54" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
+      <c r="S54" s="1"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1"/>
+      <c r="V54" s="1"/>
+      <c r="W54" s="1"/>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1"/>
+      <c r="Z54" s="2"/>
+      <c r="AA54" s="1"/>
+      <c r="AB54" s="1"/>
+      <c r="AC54" s="1"/>
+      <c r="AD54" s="1"/>
+      <c r="AE54" s="1"/>
+      <c r="AF54" s="1"/>
+      <c r="AG54" s="1"/>
+      <c r="AM54" s="1"/>
+    </row>
+    <row r="55" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="AG55" s="1"/>
+      <c r="AM55" s="1"/>
+    </row>
+    <row r="56" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="AG56" s="1"/>
+      <c r="AH56" s="1"/>
+      <c r="AI56" s="1"/>
+      <c r="AJ56" s="1"/>
+      <c r="AK56" s="1"/>
+      <c r="AL56" s="1"/>
+    </row>
+    <row r="57" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="1"/>
+      <c r="V57" s="1"/>
+      <c r="W57" s="1"/>
+      <c r="X57" s="1"/>
+      <c r="Y57" s="1"/>
+      <c r="Z57" s="2"/>
+      <c r="AA57" s="1"/>
+      <c r="AB57" s="1"/>
+      <c r="AC57" s="1"/>
+      <c r="AD57" s="1"/>
+      <c r="AE57" s="1"/>
+      <c r="AF57" s="1"/>
+      <c r="AG57" s="1"/>
+      <c r="AL57" s="1"/>
+      <c r="AM57" s="1"/>
+    </row>
+    <row r="58" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="AH58" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
